--- a/output/Data and Chart Outputs/china_nbs_capacity_utilization_quarterly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_capacity_utilization_quarterly.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chart - capacity utilisation - " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chart" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Data" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Series" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - energy and heavy indust" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chart - other manufacturing cap" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Series" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -147,383 +147,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>China capacity utilisation - other manufacturing (NBS) (to Apr/26)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Chart - capacity utilisation - '!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$B$2:$B$23</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Chart - capacity utilisation - '!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$C$2:$C$23</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Chart - capacity utilisation - '!D1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$D$2:$D$23</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Chart - capacity utilisation - '!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="EDA100"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$E$2:$E$23</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Chart - capacity utilisation - '!F1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="E87BA4"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$F$2:$F$23</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'Chart - capacity utilisation - '!G1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="008300"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$G$2:$G$23</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'Chart - capacity utilisation - '!H1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="4A3AA7"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$H$2:$H$23</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'Chart - capacity utilisation - '!I1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="E34948"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - capacity utilisation - '!$I$2:$I$23</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="low"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="1"/>
-        <tickMarkSkip val="1"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>%</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-      <spPr>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -750,11 +373,717 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>China energy and heavy industry capacity utilisation (NBS) (to Apr/26)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Chart - energy and heavy indust'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$B$2:$B$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Chart - energy and heavy indust'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$C$2:$C$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Chart - energy and heavy indust'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$D$2:$D$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Chart - energy and heavy indust'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="EDA100"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$E$2:$E$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Chart - energy and heavy indust'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E87BA4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$F$2:$F$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Chart - energy and heavy indust'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="008300"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$G$2:$G$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart - energy and heavy indust'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="4A3AA7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - energy and heavy indust'!$H$2:$H$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>China other manufacturing capacity utilisation (NBS) (to Apr/26)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Chart - other manufacturing cap'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$B$2:$B$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Chart - other manufacturing cap'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$C$2:$C$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Chart - other manufacturing cap'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$D$2:$D$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Chart - other manufacturing cap'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="EDA100"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$E$2:$E$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Chart - other manufacturing cap'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E87BA4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$F$2:$F$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Chart - other manufacturing cap'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="008300"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$G$2:$G$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart - other manufacturing cap'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="4A3AA7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$H$2:$H$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Chart - other manufacturing cap'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - other manufacturing cap'!$I$2:$I$23</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -781,7 +1110,34 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10080000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1173,7 +1529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1187,42 +1543,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Food manufacturing</t>
+          <t>Industry (total)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Mining</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>General-purpose equipment</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Special-purpose equipment</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Automobiles</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Electrical machinery and equipment</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Computers, communication and electronic equipment</t>
+          <t>Power, heat, gas and water supply</t>
         </is>
       </c>
     </row>
@@ -1231,28 +1567,16 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>74.2</v>
+        <v>77.2</v>
       </c>
       <c r="C2" t="n">
-        <v>78.3</v>
+        <v>75.3</v>
       </c>
       <c r="D2" t="n">
-        <v>76.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
-      </c>
-      <c r="F2" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>79.3</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="3">
@@ -1260,28 +1584,16 @@
         <v>44287</v>
       </c>
       <c r="B3" t="n">
-        <v>72.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>80.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="E3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="F3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>79.09999999999999</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="4">
@@ -1289,28 +1601,16 @@
         <v>44378</v>
       </c>
       <c r="B4" t="n">
-        <v>74.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>79.5</v>
+        <v>76</v>
       </c>
       <c r="D4" t="n">
-        <v>76.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="E4" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="F4" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>81</v>
-      </c>
-      <c r="I4" t="n">
-        <v>80.8</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="5">
@@ -1318,28 +1618,16 @@
         <v>44470</v>
       </c>
       <c r="B5" t="n">
-        <v>74.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>79.2</v>
+        <v>77</v>
       </c>
       <c r="D5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="F5" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="G5" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>81.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1347,28 +1635,16 @@
         <v>44562</v>
       </c>
       <c r="B6" t="n">
-        <v>71.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="C6" t="n">
-        <v>78.2</v>
+        <v>77</v>
       </c>
       <c r="D6" t="n">
-        <v>74.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>77</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="7">
@@ -1376,28 +1652,16 @@
         <v>44652</v>
       </c>
       <c r="B7" t="n">
-        <v>71.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>77.8</v>
+        <v>76.7</v>
       </c>
       <c r="D7" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>76</v>
-      </c>
-      <c r="I7" t="n">
-        <v>77.5</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1405,28 +1669,16 @@
         <v>44743</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>76.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>74.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="G8" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>78.09999999999999</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="9">
@@ -1434,28 +1686,16 @@
         <v>44835</v>
       </c>
       <c r="B9" t="n">
-        <v>71.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="C9" t="n">
-        <v>76.2</v>
+        <v>76.5</v>
       </c>
       <c r="D9" t="n">
-        <v>77.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="E9" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>79</v>
-      </c>
-      <c r="I9" t="n">
-        <v>78.5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -1463,28 +1703,16 @@
         <v>44927</v>
       </c>
       <c r="B10" t="n">
-        <v>70.7</v>
+        <v>74.3</v>
       </c>
       <c r="C10" t="n">
-        <v>75.5</v>
+        <v>75.2</v>
       </c>
       <c r="D10" t="n">
-        <v>75.2</v>
+        <v>74.5</v>
       </c>
       <c r="E10" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="F10" t="n">
-        <v>77</v>
-      </c>
-      <c r="G10" t="n">
-        <v>72</v>
-      </c>
-      <c r="H10" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>73.7</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1492,28 +1720,16 @@
         <v>45017</v>
       </c>
       <c r="B11" t="n">
-        <v>68.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="C11" t="n">
-        <v>76.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D11" t="n">
-        <v>76.2</v>
+        <v>74.8</v>
       </c>
       <c r="E11" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="F11" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="G11" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>74.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1521,28 +1737,16 @@
         <v>45108</v>
       </c>
       <c r="B12" t="n">
-        <v>71.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>76.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>72.7</v>
+        <v>75.8</v>
       </c>
       <c r="E12" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>76.5</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="13">
@@ -1550,28 +1754,16 @@
         <v>45200</v>
       </c>
       <c r="B13" t="n">
-        <v>71.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>76.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>75.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>77.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1579,115 +1771,58 @@
         <v>45292</v>
       </c>
       <c r="B14" t="n">
-        <v>69.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>73.8</v>
       </c>
       <c r="E14" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>77</v>
-      </c>
-      <c r="G14" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="H14" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>74.7</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>45383</v>
       </c>
-      <c r="B15" t="n">
-        <v>68.8</v>
-      </c>
       <c r="C15" t="n">
-        <v>79.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="E15" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="F15" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>73</v>
-      </c>
-      <c r="H15" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>76.2</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
         <v>45474</v>
       </c>
-      <c r="B16" t="n">
-        <v>70.7</v>
-      </c>
       <c r="C16" t="n">
-        <v>77.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>73.8</v>
+        <v>75.2</v>
       </c>
       <c r="E16" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="F16" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>77.90000000000001</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>45566</v>
       </c>
-      <c r="B17" t="n">
-        <v>70.7</v>
-      </c>
       <c r="C17" t="n">
-        <v>78.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>75.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="F17" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="G17" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="I17" t="n">
-        <v>79.40000000000001</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="18">
@@ -1695,28 +1830,16 @@
         <v>45658</v>
       </c>
       <c r="B18" t="n">
-        <v>69.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>77.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>72.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="F18" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="G18" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="I18" t="n">
-        <v>74.7</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1724,28 +1847,16 @@
         <v>45748</v>
       </c>
       <c r="B19" t="n">
-        <v>69.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="C19" t="n">
-        <v>77.8</v>
+        <v>72.7</v>
       </c>
       <c r="D19" t="n">
-        <v>72.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="E19" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="F19" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>77.3</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="20">
@@ -1753,28 +1864,16 @@
         <v>45839</v>
       </c>
       <c r="B20" t="n">
-        <v>70.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>77.2</v>
+        <v>72.5</v>
       </c>
       <c r="D20" t="n">
-        <v>71.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="E20" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="F20" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="H20" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>79</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="21">
@@ -1782,28 +1881,16 @@
         <v>45931</v>
       </c>
       <c r="B21" t="n">
-        <v>68.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>77.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="D21" t="n">
-        <v>72.8</v>
+        <v>75.2</v>
       </c>
       <c r="E21" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="F21" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="G21" t="n">
-        <v>76</v>
-      </c>
-      <c r="H21" t="n">
-        <v>75</v>
-      </c>
-      <c r="I21" t="n">
-        <v>79.7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
@@ -1811,28 +1898,16 @@
         <v>46023</v>
       </c>
       <c r="B22" t="n">
-        <v>70</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>76.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>72.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
-      </c>
-      <c r="F22" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="G22" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>75.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1840,28 +1915,16 @@
         <v>46113</v>
       </c>
       <c r="B23" t="n">
-        <v>70.2</v>
+        <v>73</v>
       </c>
       <c r="C23" t="n">
-        <v>74.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>71.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="E23" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="F23" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="G23" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="H23" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="I23" t="n">
-        <v>78.7</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1876,7 +1939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1890,22 +1953,37 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Industry (total)</t>
+          <t>Coal mining and washing</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Mining</t>
+          <t>Oil and gas extraction</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Chemical raw materials and products</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Power, heat, gas and water supply</t>
+          <t>Chemical fibres</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Non-metallic mineral products (cement, glass)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ferrous metal smelting and rolling (steel)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Non-ferrous metal smelting and rolling</t>
         </is>
       </c>
     </row>
@@ -1914,16 +1992,25 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>77.2</v>
+        <v>72.5</v>
       </c>
       <c r="C2" t="n">
-        <v>75.3</v>
+        <v>90</v>
       </c>
       <c r="D2" t="n">
-        <v>77.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>74.5</v>
+        <v>87.09999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>80.3</v>
       </c>
     </row>
     <row r="3">
@@ -1931,16 +2018,25 @@
         <v>44287</v>
       </c>
       <c r="B3" t="n">
-        <v>78.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>76.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="D3" t="n">
-        <v>78.8</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>74.7</v>
+        <v>85.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1948,16 +2044,25 @@
         <v>44378</v>
       </c>
       <c r="B4" t="n">
-        <v>77.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="C4" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D4" t="n">
-        <v>77.3</v>
+        <v>77.8</v>
       </c>
       <c r="E4" t="n">
-        <v>75.3</v>
+        <v>83.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70</v>
+      </c>
+      <c r="G4" t="n">
+        <v>77</v>
+      </c>
+      <c r="H4" t="n">
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1965,16 +2070,25 @@
         <v>44470</v>
       </c>
       <c r="B5" t="n">
-        <v>77.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D5" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>75.40000000000001</v>
+        <v>82.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1982,16 +2096,25 @@
         <v>44562</v>
       </c>
       <c r="B6" t="n">
-        <v>75.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C6" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="G6" t="n">
         <v>77</v>
       </c>
-      <c r="D6" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>73.8</v>
+      <c r="H6" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -1999,16 +2122,25 @@
         <v>44652</v>
       </c>
       <c r="B7" t="n">
-        <v>75.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="C7" t="n">
-        <v>76.7</v>
+        <v>92.3</v>
       </c>
       <c r="D7" t="n">
-        <v>75.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="E7" t="n">
-        <v>70.59999999999999</v>
+        <v>83.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -2016,16 +2148,25 @@
         <v>44743</v>
       </c>
       <c r="B8" t="n">
-        <v>75.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>76.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D8" t="n">
-        <v>75.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E8" t="n">
-        <v>72.7</v>
+        <v>82</v>
+      </c>
+      <c r="F8" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2033,16 +2174,25 @@
         <v>44835</v>
       </c>
       <c r="B9" t="n">
-        <v>75.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>76.5</v>
+        <v>91.3</v>
       </c>
       <c r="D9" t="n">
-        <v>75.8</v>
+        <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>79.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2050,16 +2200,25 @@
         <v>44927</v>
       </c>
       <c r="B10" t="n">
-        <v>74.3</v>
+        <v>73.8</v>
       </c>
       <c r="C10" t="n">
-        <v>75.2</v>
+        <v>91.2</v>
       </c>
       <c r="D10" t="n">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="E10" t="n">
-        <v>71.90000000000001</v>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>77.8</v>
       </c>
     </row>
     <row r="11">
@@ -2070,13 +2229,22 @@
         <v>74.5</v>
       </c>
       <c r="C11" t="n">
-        <v>74.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>74.8</v>
+        <v>74.3</v>
       </c>
       <c r="E11" t="n">
-        <v>71.40000000000001</v>
+        <v>84.09999999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>79</v>
+      </c>
+      <c r="H11" t="n">
+        <v>80.3</v>
       </c>
     </row>
     <row r="12">
@@ -2084,16 +2252,25 @@
         <v>45108</v>
       </c>
       <c r="B12" t="n">
-        <v>75.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="C12" t="n">
-        <v>75.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="D12" t="n">
-        <v>75.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>74.2</v>
+        <v>85.09999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>65</v>
+      </c>
+      <c r="G12" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>80.2</v>
       </c>
     </row>
     <row r="13">
@@ -2101,16 +2278,25 @@
         <v>45200</v>
       </c>
       <c r="B13" t="n">
-        <v>75.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>77.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>76.7</v>
       </c>
       <c r="E13" t="n">
-        <v>74.40000000000001</v>
+        <v>85.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2118,58 +2304,103 @@
         <v>45292</v>
       </c>
       <c r="B14" t="n">
-        <v>73.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>91.7</v>
       </c>
       <c r="D14" t="n">
-        <v>73.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>71.2</v>
+        <v>85.59999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>62</v>
+      </c>
+      <c r="G14" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>78.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>45383</v>
       </c>
+      <c r="B15" t="n">
+        <v>72.8</v>
+      </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>91.8</v>
       </c>
       <c r="D15" t="n">
-        <v>75.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>71.40000000000001</v>
+        <v>85</v>
+      </c>
+      <c r="F15" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
         <v>45474</v>
       </c>
+      <c r="B16" t="n">
+        <v>72.7</v>
+      </c>
       <c r="C16" t="n">
-        <v>74.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="D16" t="n">
-        <v>75.2</v>
+        <v>76</v>
       </c>
       <c r="E16" t="n">
-        <v>74.3</v>
+        <v>85.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>45566</v>
       </c>
+      <c r="B17" t="n">
+        <v>73.90000000000001</v>
+      </c>
       <c r="C17" t="n">
-        <v>75.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="D17" t="n">
         <v>76.40000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>74.8</v>
+        <v>85.59999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>79.3</v>
       </c>
     </row>
     <row r="18">
@@ -2177,16 +2408,25 @@
         <v>45658</v>
       </c>
       <c r="B18" t="n">
-        <v>74.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>74.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>74.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="E18" t="n">
-        <v>73.59999999999999</v>
+        <v>86.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>77.5</v>
       </c>
     </row>
     <row r="19">
@@ -2194,16 +2434,25 @@
         <v>45748</v>
       </c>
       <c r="B19" t="n">
-        <v>74</v>
+        <v>69.3</v>
       </c>
       <c r="C19" t="n">
-        <v>72.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>74.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>71.5</v>
+        <v>85.59999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>77.7</v>
       </c>
     </row>
     <row r="20">
@@ -2211,16 +2460,25 @@
         <v>45839</v>
       </c>
       <c r="B20" t="n">
-        <v>74.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="C20" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="D20" t="n">
         <v>72.5</v>
       </c>
-      <c r="D20" t="n">
-        <v>74.8</v>
-      </c>
       <c r="E20" t="n">
-        <v>74.3</v>
+        <v>85.59999999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>62</v>
+      </c>
+      <c r="G20" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>77.8</v>
       </c>
     </row>
     <row r="21">
@@ -2228,16 +2486,25 @@
         <v>45931</v>
       </c>
       <c r="B21" t="n">
-        <v>74.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>71.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>75.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>74</v>
+        <v>85.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>75.8</v>
       </c>
     </row>
     <row r="22">
@@ -2245,16 +2512,25 @@
         <v>46023</v>
       </c>
       <c r="B22" t="n">
-        <v>73.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>72.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D22" t="n">
-        <v>73.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="E22" t="n">
-        <v>71.90000000000001</v>
+        <v>84.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>77.2</v>
       </c>
     </row>
     <row r="23">
@@ -2262,16 +2538,25 @@
         <v>46113</v>
       </c>
       <c r="B23" t="n">
-        <v>73</v>
+        <v>61.2</v>
       </c>
       <c r="C23" t="n">
-        <v>69.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="D23" t="n">
-        <v>73.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>70.40000000000001</v>
+        <v>84.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>76.2</v>
       </c>
     </row>
   </sheetData>
@@ -2286,6 +2571,709 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Food manufacturing</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>General-purpose equipment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Special-purpose equipment</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Electrical machinery and equipment</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Computers, communication and electronic equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>79.09999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B4" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>81</v>
+      </c>
+      <c r="I4" t="n">
+        <v>80.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B5" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>81.59999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B6" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B7" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>76</v>
+      </c>
+      <c r="I7" t="n">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B8" t="n">
+        <v>72</v>
+      </c>
+      <c r="C8" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>78.09999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B9" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>79</v>
+      </c>
+      <c r="I9" t="n">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B10" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>77</v>
+      </c>
+      <c r="G10" t="n">
+        <v>72</v>
+      </c>
+      <c r="H10" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B11" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>74.59999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B12" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B13" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>77.59999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B14" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>78</v>
+      </c>
+      <c r="D14" t="n">
+        <v>76</v>
+      </c>
+      <c r="E14" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>77</v>
+      </c>
+      <c r="G14" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B15" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>73</v>
+      </c>
+      <c r="H15" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B16" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>77.90000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B17" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>79.40000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B18" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B19" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B20" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B21" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>76</v>
+      </c>
+      <c r="H21" t="n">
+        <v>75</v>
+      </c>
+      <c r="I21" t="n">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B22" t="n">
+        <v>70</v>
+      </c>
+      <c r="C22" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>79</v>
+      </c>
+      <c r="F22" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="G22" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>75.40000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B23" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="D23" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>78.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3751,7 +4739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3913,7 +4901,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>capacity utilisation - energy and heavy industry</t>
+          <t>energy and heavy industry capacity utilisation</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3940,7 +4928,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>capacity utilisation - energy and heavy industry</t>
+          <t>energy and heavy industry capacity utilisation</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3967,7 +4955,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>capacity utilisation - energy and heavy industry</t>
+          <t>energy and heavy industry capacity utilisation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3994,7 +4982,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>capacity utilisation - energy and heavy industry</t>
+          <t>energy and heavy industry capacity utilisation</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4021,7 +5009,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>capacity utilisation - energy and heavy industry</t>
+          <t>energy and heavy industry capacity utilisation</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4048,7 +5036,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>capacity utilisation - energy and heavy industry</t>
+          <t>energy and heavy industry capacity utilisation</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4075,7 +5063,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>capacity utilisation - energy and heavy industry</t>
+          <t>energy and heavy industry capacity utilisation</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4102,7 +5090,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>capacity utilisation - other manufacturing</t>
+          <t>other manufacturing capacity utilisation</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4129,7 +5117,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>capacity utilisation - other manufacturing</t>
+          <t>other manufacturing capacity utilisation</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4156,7 +5144,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>capacity utilisation - other manufacturing</t>
+          <t>other manufacturing capacity utilisation</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4183,7 +5171,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>capacity utilisation - other manufacturing</t>
+          <t>other manufacturing capacity utilisation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4210,7 +5198,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>capacity utilisation - other manufacturing</t>
+          <t>other manufacturing capacity utilisation</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4237,7 +5225,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>capacity utilisation - other manufacturing</t>
+          <t>other manufacturing capacity utilisation</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4264,7 +5252,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>capacity utilisation - other manufacturing</t>
+          <t>other manufacturing capacity utilisation</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4291,7 +5279,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>capacity utilisation - other manufacturing</t>
+          <t>other manufacturing capacity utilisation</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/output/Data and Chart Outputs/china_nbs_capacity_utilization_quarterly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_capacity_utilization_quarterly.xlsx
@@ -21,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -163,6 +163,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -320,11 +321,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -352,14 +365,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -390,6 +411,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -655,11 +677,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -687,14 +721,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -725,6 +767,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -1026,11 +1069,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -1058,14 +1113,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1476,6 +1539,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1490,6 +1554,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1504,6 +1569,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1563,7 +1629,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1580,7 +1646,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -1597,7 +1663,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B4" t="n">
@@ -1614,7 +1680,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B5" t="n">
@@ -1631,7 +1697,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B6" t="n">
@@ -1648,7 +1714,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B7" t="n">
@@ -1665,7 +1731,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B8" t="n">
@@ -1682,7 +1748,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B9" t="n">
@@ -1699,7 +1765,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B10" t="n">
@@ -1716,7 +1782,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B11" t="n">
@@ -1733,7 +1799,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B12" t="n">
@@ -1750,7 +1816,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B13" t="n">
@@ -1767,7 +1833,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B14" t="n">
@@ -1784,7 +1850,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B15" t="n">
@@ -1801,7 +1867,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B16" t="n">
@@ -1818,7 +1884,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B17" t="n">
@@ -1835,7 +1901,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B18" t="n">
@@ -1852,7 +1918,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B19" t="n">
@@ -1869,7 +1935,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B20" t="n">
@@ -1886,7 +1952,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B21" t="n">
@@ -1903,7 +1969,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1920,7 +1986,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B23" t="n">
@@ -1997,7 +2063,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -2023,7 +2089,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -2049,7 +2115,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B4" t="n">
@@ -2075,7 +2141,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B5" t="n">
@@ -2101,7 +2167,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B6" t="n">
@@ -2127,7 +2193,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B7" t="n">
@@ -2153,7 +2219,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B8" t="n">
@@ -2179,7 +2245,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B9" t="n">
@@ -2205,7 +2271,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B10" t="n">
@@ -2231,7 +2297,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B11" t="n">
@@ -2257,7 +2323,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B12" t="n">
@@ -2283,7 +2349,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B13" t="n">
@@ -2309,7 +2375,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B14" t="n">
@@ -2335,7 +2401,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B15" t="n">
@@ -2361,7 +2427,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B16" t="n">
@@ -2387,7 +2453,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B17" t="n">
@@ -2413,7 +2479,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B18" t="n">
@@ -2439,7 +2505,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B19" t="n">
@@ -2465,7 +2531,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B20" t="n">
@@ -2491,7 +2557,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B21" t="n">
@@ -2517,7 +2583,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -2543,7 +2609,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B23" t="n">
@@ -2634,7 +2700,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -2663,7 +2729,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -2692,7 +2758,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B4" t="n">
@@ -2721,7 +2787,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B5" t="n">
@@ -2750,7 +2816,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B6" t="n">
@@ -2779,7 +2845,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B7" t="n">
@@ -2808,7 +2874,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B8" t="n">
@@ -2837,7 +2903,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B9" t="n">
@@ -2866,7 +2932,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B10" t="n">
@@ -2895,7 +2961,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B11" t="n">
@@ -2924,7 +2990,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B12" t="n">
@@ -2953,7 +3019,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B13" t="n">
@@ -2982,7 +3048,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B14" t="n">
@@ -3011,7 +3077,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B15" t="n">
@@ -3040,7 +3106,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B16" t="n">
@@ -3069,7 +3135,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B17" t="n">
@@ -3098,7 +3164,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B18" t="n">
@@ -3127,7 +3193,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B19" t="n">
@@ -3156,7 +3222,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B20" t="n">
@@ -3185,7 +3251,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B21" t="n">
@@ -3214,7 +3280,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -3243,7 +3309,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B23" t="n">

--- a/output/Data and Chart Outputs/china_nbs_capacity_utilization_quarterly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_capacity_utilization_quarterly.xlsx
@@ -159,7 +159,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China industrial capacity utilisation (NBS) (to Apr/26)</a:t>
+              <a:t>China industrial capacity utilisation (NBS) (to Jul/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -195,12 +195,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$36</f>
+              <f>'Chart'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$36</f>
+              <f>'Chart'!$B$2:$B$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -231,12 +231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$36</f>
+              <f>'Chart'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$36</f>
+              <f>'Chart'!$C$2:$C$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -267,12 +267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$36</f>
+              <f>'Chart'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$36</f>
+              <f>'Chart'!$D$2:$D$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -303,12 +303,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$36</f>
+              <f>'Chart'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$36</f>
+              <f>'Chart'!$E$2:$E$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -341,8 +341,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-        <tickMarkSkip val="2"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -408,7 +408,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China energy and heavy industry capacity utilisation (NBS) (to Apr/26)</a:t>
+              <a:t>China energy and heavy industry capacity utilisation (NBS) (to Jul/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$A$2:$A$36</f>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$B$2:$B$36</f>
+              <f>'Chart - energy and heavy indust'!$B$2:$B$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -480,12 +480,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$A$2:$A$36</f>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$C$2:$C$36</f>
+              <f>'Chart - energy and heavy indust'!$C$2:$C$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -516,12 +516,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$A$2:$A$36</f>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$D$2:$D$36</f>
+              <f>'Chart - energy and heavy indust'!$D$2:$D$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -552,12 +552,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$A$2:$A$36</f>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$E$2:$E$36</f>
+              <f>'Chart - energy and heavy indust'!$E$2:$E$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -588,12 +588,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$A$2:$A$36</f>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$F$2:$F$36</f>
+              <f>'Chart - energy and heavy indust'!$F$2:$F$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -624,12 +624,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$A$2:$A$36</f>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$G$2:$G$36</f>
+              <f>'Chart - energy and heavy indust'!$G$2:$G$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -660,12 +660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$A$2:$A$36</f>
+              <f>'Chart - energy and heavy indust'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy and heavy indust'!$H$2:$H$36</f>
+              <f>'Chart - energy and heavy indust'!$H$2:$H$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -698,8 +698,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-        <tickMarkSkip val="2"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -765,7 +765,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China other manufacturing capacity utilisation (NBS) (to Apr/26)</a:t>
+              <a:t>China other manufacturing capacity utilisation (NBS) (to Jul/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -801,12 +801,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$A$2:$A$36</f>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$B$2:$B$36</f>
+              <f>'Chart - other manufacturing cap'!$B$2:$B$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -837,12 +837,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$A$2:$A$36</f>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$C$2:$C$36</f>
+              <f>'Chart - other manufacturing cap'!$C$2:$C$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -873,12 +873,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$A$2:$A$36</f>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$D$2:$D$36</f>
+              <f>'Chart - other manufacturing cap'!$D$2:$D$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -909,12 +909,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$A$2:$A$36</f>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$E$2:$E$36</f>
+              <f>'Chart - other manufacturing cap'!$E$2:$E$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -945,12 +945,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$A$2:$A$36</f>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$F$2:$F$36</f>
+              <f>'Chart - other manufacturing cap'!$F$2:$F$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -981,12 +981,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$A$2:$A$36</f>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$G$2:$G$36</f>
+              <f>'Chart - other manufacturing cap'!$G$2:$G$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1017,12 +1017,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$A$2:$A$36</f>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$H$2:$H$36</f>
+              <f>'Chart - other manufacturing cap'!$H$2:$H$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1053,12 +1053,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$A$2:$A$36</f>
+              <f>'Chart - other manufacturing cap'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - other manufacturing cap'!$I$2:$I$36</f>
+              <f>'Chart - other manufacturing cap'!$I$2:$I$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1091,8 +1091,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-        <tickMarkSkip val="2"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1598,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2224,6 +2224,23 @@
       </c>
       <c r="E36" t="n">
         <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B37" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>72.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2238,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3194,6 +3211,32 @@
       </c>
       <c r="H36" t="n">
         <v>76.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B37" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D37" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>73.5</v>
       </c>
     </row>
   </sheetData>
@@ -3208,7 +3251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4274,6 +4317,35 @@
       </c>
       <c r="I36" t="n">
         <v>78.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B37" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="D37" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F37" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G37" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="I37" t="n">
+        <v>80.2</v>
       </c>
     </row>
   </sheetData>
@@ -4288,7 +4360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY36"/>
+  <dimension ref="A1:BY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11805,6 +11877,239 @@
       </c>
       <c r="BY36" t="n">
         <v>1.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B37" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="F37" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="I37" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="L37" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="O37" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="R37" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="T37" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V37" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>64</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>71</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>77</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>69</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
